--- a/Aida_Perramon-Malavez/TLRHEUROPE-D-25-00124/admissionsED.xlsx
+++ b/Aida_Perramon-Malavez/TLRHEUROPE-D-25-00124/admissionsED.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upcbcntech-my.sharepoint.com/personal/aida_perramon_office365_upc_edu/Documents/Escritorio/BIOCOM-SC/Danilo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_16E57E1A9267120E62355476585DCE3A87465525" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05401940-AACD-4379-8D21-24A8DAFFBDFB}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_16E57E1A9267120E62355476585DCE3A87465525" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E51B2C18-850C-4312-BCB6-A20453C7AF54}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,9 +26,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="25">
   <si>
     <t>all_diag</t>
-  </si>
-  <si>
-    <t>rvi</t>
   </si>
   <si>
     <t>bronquis</t>
@@ -98,6 +95,9 @@
   </si>
   <si>
     <t>age_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respiratory Diasgnoses (not including Bronchiolitis) </t>
   </si>
 </sst>
 </file>
@@ -173,10 +173,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,45 +460,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J145"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>21558</v>
@@ -520,21 +515,21 @@
         <v>10.223582892661661</v>
       </c>
       <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
         <v>9</v>
-      </c>
-      <c r="I2" t="s">
-        <v>10</v>
       </c>
       <c r="J2">
         <v>82.238805970149258</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>4046</v>
@@ -552,21 +547,21 @@
         <v>10.94908551655957</v>
       </c>
       <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
         <v>9</v>
-      </c>
-      <c r="I3" t="s">
-        <v>10</v>
       </c>
       <c r="J3">
         <v>37.19563392107473</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>7540</v>
@@ -584,21 +579,21 @@
         <v>2.7718832891246681</v>
       </c>
       <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" t="s">
         <v>9</v>
-      </c>
-      <c r="I4" t="s">
-        <v>10</v>
       </c>
       <c r="J4">
         <v>13.253012048192771</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>23444</v>
@@ -616,21 +611,21 @@
         <v>0.22607063641016889</v>
       </c>
       <c r="H5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" t="s">
         <v>9</v>
-      </c>
-      <c r="I5" t="s">
-        <v>10</v>
       </c>
       <c r="J5">
         <v>2.2659256092347162</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>20771</v>
@@ -648,21 +643,21 @@
         <v>9.0655240479514703</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>83.688888888888897</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>3088</v>
@@ -680,21 +675,21 @@
         <v>13.01813471502591</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>46.689895470383277</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>5503</v>
@@ -712,21 +707,21 @@
         <v>4.0886789024168628</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>18.734388009991669</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9">
         <v>17851</v>
@@ -744,21 +739,21 @@
         <v>0.25208671783093378</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>2.506963788300836</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>18862</v>
@@ -776,21 +771,21 @@
         <v>3.7959919414696222</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>83.644859813084111</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>2596</v>
@@ -808,21 +803,21 @@
         <v>10.59322033898305</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>59.395248380129587</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12">
         <v>5257</v>
@@ -840,21 +835,21 @@
         <v>4.6224082176146091</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>26.499454743729551</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>18061</v>
@@ -872,21 +867,21 @@
         <v>0.19378771939538231</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>2.6375282592313489</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>20751</v>
@@ -904,21 +899,21 @@
         <v>7.8116717266637758</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>80.807577268195416</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15">
         <v>3185</v>
@@ -936,21 +931,21 @@
         <v>13.877551020408159</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>49.496080627099673</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16">
         <v>6190</v>
@@ -968,21 +963,21 @@
         <v>5.395799676898223</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>22.017139090309819</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17">
         <v>21504</v>
@@ -1000,21 +995,21 @@
         <v>0.36737351190476192</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>3.26581231914014</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18">
         <v>22396</v>
@@ -1032,21 +1027,21 @@
         <v>10.89926772637971</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>82.243935309973054</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19">
         <v>4124</v>
@@ -1064,21 +1059,21 @@
         <v>14.88845780795344</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>46.621108580106302</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20">
         <v>7239</v>
@@ -1096,21 +1091,21 @@
         <v>5.1388313302942397</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>20.586607636967351</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21">
         <v>23334</v>
@@ -1128,21 +1123,21 @@
         <v>0.4157024085026142</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>3.2539416303253939</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22">
         <v>19321</v>
@@ -1160,21 +1155,21 @@
         <v>4.9272811966254331</v>
       </c>
       <c r="H22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J22">
         <v>69.897209985315712</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>3352</v>
@@ -1192,21 +1187,21 @@
         <v>14.28997613365155</v>
       </c>
       <c r="H23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>45.359848484848477</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>6596</v>
@@ -1224,21 +1219,21 @@
         <v>4.4572468162522743</v>
       </c>
       <c r="H24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>18.260869565217391</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>21266</v>
@@ -1256,21 +1251,21 @@
         <v>0.20220069594658141</v>
       </c>
       <c r="H25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>1.7151974471479861</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>388</v>
@@ -1288,21 +1283,21 @@
         <v>12.88659793814433</v>
       </c>
       <c r="H26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J26">
         <v>89.285714285714292</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27">
         <v>75</v>
@@ -1320,21 +1315,21 @@
         <v>14.66666666666667</v>
       </c>
       <c r="H27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J27">
         <v>64.705882352941174</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28">
         <v>140</v>
@@ -1352,21 +1347,21 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="H28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J28">
         <v>14.81481481481481</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29">
         <v>230</v>
@@ -1384,21 +1379,21 @@
         <v>0.43478260869565222</v>
       </c>
       <c r="H29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J29">
         <v>2.9411764705882351</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30">
         <v>328</v>
@@ -1416,21 +1411,21 @@
         <v>11.280487804878049</v>
       </c>
       <c r="H30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J30">
         <v>88.095238095238088</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31">
         <v>66</v>
@@ -1448,21 +1443,21 @@
         <v>15.15151515151515</v>
       </c>
       <c r="H31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J31">
         <v>62.5</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C32">
         <v>106</v>
@@ -1480,21 +1475,21 @@
         <v>5.6603773584905666</v>
       </c>
       <c r="H32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J32">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33">
         <v>205</v>
@@ -1512,21 +1507,21 @@
         <v>0.48780487804878048</v>
       </c>
       <c r="H33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J33">
         <v>3.5714285714285712</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34">
         <v>283</v>
@@ -1544,21 +1539,21 @@
         <v>0.70671378091872794</v>
       </c>
       <c r="H34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J34">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35">
         <v>52</v>
@@ -1576,21 +1571,21 @@
         <v>3.8461538461538458</v>
       </c>
       <c r="H35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J35">
         <v>66.666666666666657</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36">
         <v>75</v>
@@ -1608,21 +1603,21 @@
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37">
         <v>149</v>
@@ -1640,21 +1635,21 @@
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38">
         <v>289</v>
@@ -1672,21 +1667,21 @@
         <v>16.262975778546711</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J38">
         <v>88.679245283018872</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C39">
         <v>65</v>
@@ -1704,21 +1699,21 @@
         <v>21.53846153846154</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J39">
         <v>77.777777777777786</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40">
         <v>111</v>
@@ -1736,21 +1731,21 @@
         <v>9.0090090090090094</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J40">
         <v>58.82352941176471</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C41">
         <v>208</v>
@@ -1768,21 +1763,21 @@
         <v>1.4423076923076921</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J41">
         <v>13.63636363636363</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42">
         <v>337</v>
@@ -1800,21 +1795,21 @@
         <v>21.958456973293771</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J42">
         <v>92.5</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C43">
         <v>57</v>
@@ -1832,21 +1827,21 @@
         <v>15.789473684210529</v>
       </c>
       <c r="H43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J43">
         <v>81.818181818181827</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44">
         <v>110</v>
@@ -1864,21 +1859,21 @@
         <v>5.4545454545454541</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J44">
         <v>26.086956521739129</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45">
         <v>188</v>
@@ -1896,21 +1891,21 @@
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C46">
         <v>343</v>
@@ -1928,21 +1923,21 @@
         <v>16.618075801749271</v>
       </c>
       <c r="H46" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" t="s">
         <v>18</v>
-      </c>
-      <c r="I46" t="s">
-        <v>19</v>
       </c>
       <c r="J46">
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C47">
         <v>75</v>
@@ -1960,21 +1955,21 @@
         <v>24</v>
       </c>
       <c r="H47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" t="s">
         <v>18</v>
-      </c>
-      <c r="I47" t="s">
-        <v>19</v>
       </c>
       <c r="J47">
         <v>78.260869565217391</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C48">
         <v>111</v>
@@ -1992,21 +1987,21 @@
         <v>5.4054054054054053</v>
       </c>
       <c r="H48" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" t="s">
         <v>18</v>
-      </c>
-      <c r="I48" t="s">
-        <v>19</v>
       </c>
       <c r="J48">
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49">
         <v>161</v>
@@ -2024,21 +2019,21 @@
         <v>0</v>
       </c>
       <c r="H49" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" t="s">
         <v>18</v>
-      </c>
-      <c r="I49" t="s">
-        <v>19</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C50">
         <v>972</v>
@@ -2056,21 +2051,21 @@
         <v>32.098765432098773</v>
       </c>
       <c r="H50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J50">
         <v>89.398280802292263</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C51">
         <v>383</v>
@@ -2088,21 +2083,21 @@
         <v>32.375979112271537</v>
       </c>
       <c r="H51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J51">
         <v>69.662921348314612</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C52">
         <v>686</v>
@@ -2120,21 +2115,21 @@
         <v>7.4344023323615156</v>
       </c>
       <c r="H52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J52">
         <v>15.74074074074074</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53">
         <v>1255</v>
@@ -2152,21 +2147,21 @@
         <v>0.9561752988047808</v>
       </c>
       <c r="H53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J53">
         <v>3.2345013477088949</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C54">
         <v>995</v>
@@ -2184,21 +2179,21 @@
         <v>31.457286432160799</v>
       </c>
       <c r="H54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J54">
         <v>87.186629526462397</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55">
         <v>406</v>
@@ -2216,21 +2211,21 @@
         <v>41.379310344827587</v>
       </c>
       <c r="H55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J55">
         <v>74.336283185840713</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C56">
         <v>654</v>
@@ -2248,21 +2243,21 @@
         <v>3.9755351681957189</v>
       </c>
       <c r="H56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J56">
         <v>7.951070336391437</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57">
         <v>1257</v>
@@ -2280,21 +2275,21 @@
         <v>0.1591089896579157</v>
       </c>
       <c r="H57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J57">
         <v>0.47393364928909948</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58">
         <v>634</v>
@@ -2312,21 +2307,21 @@
         <v>3.6277602523659311</v>
       </c>
       <c r="H58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J58">
         <v>54.761904761904773</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C59">
         <v>208</v>
@@ -2344,21 +2339,21 @@
         <v>15.38461538461539</v>
       </c>
       <c r="H59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J59">
         <v>82.051282051282044</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60">
         <v>384</v>
@@ -2376,21 +2371,21 @@
         <v>2.864583333333333</v>
       </c>
       <c r="H60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J60">
         <v>11.956521739130441</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C61">
         <v>747</v>
@@ -2408,21 +2403,21 @@
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C62">
         <v>907</v>
@@ -2440,21 +2435,21 @@
         <v>25.799338478500552</v>
       </c>
       <c r="H62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J62">
         <v>85.40145985401459</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C63">
         <v>359</v>
@@ -2472,21 +2467,21 @@
         <v>37.047353760445681</v>
       </c>
       <c r="H63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J63">
         <v>73.480662983425418</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64">
         <v>602</v>
@@ -2504,21 +2499,21 @@
         <v>5.3156146179402004</v>
       </c>
       <c r="H64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J64">
         <v>11.46953405017921</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65">
         <v>1132</v>
@@ -2536,21 +2531,21 @@
         <v>0.17667844522968201</v>
       </c>
       <c r="H65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J65">
         <v>0.60790273556231</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C66">
         <v>962</v>
@@ -2568,21 +2563,21 @@
         <v>33.471933471933482</v>
       </c>
       <c r="H66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J66">
         <v>88.219178082191789</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67">
         <v>366</v>
@@ -2600,21 +2595,21 @@
         <v>40.710382513661202</v>
       </c>
       <c r="H67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J67">
         <v>76.80412371134021</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C68">
         <v>575</v>
@@ -2632,21 +2627,21 @@
         <v>11.130434782608701</v>
       </c>
       <c r="H68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J68">
         <v>26.016260162601629</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C69">
         <v>1176</v>
@@ -2664,21 +2659,21 @@
         <v>0.51020408163265307</v>
       </c>
       <c r="H69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J69">
         <v>1.834862385321101</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C70">
         <v>991</v>
@@ -2696,21 +2691,21 @@
         <v>32.391523713420789</v>
       </c>
       <c r="H70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J70">
         <v>86.290322580645167</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C71">
         <v>363</v>
@@ -2728,21 +2723,21 @@
         <v>42.424242424242422</v>
       </c>
       <c r="H71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I71" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J71">
         <v>77.777777777777786</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C72">
         <v>576</v>
@@ -2760,21 +2755,21 @@
         <v>9.5486111111111107</v>
       </c>
       <c r="H72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J72">
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C73">
         <v>1243</v>
@@ -2792,10 +2787,10 @@
         <v>0.40225261464199519</v>
       </c>
       <c r="H73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J73">
         <v>1.1235955056179781</v>
@@ -2806,7 +2801,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C74">
         <v>1539</v>
@@ -2824,10 +2819,10 @@
         <v>27.030539311241061</v>
       </c>
       <c r="H74" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I74" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J74">
         <v>81.568627450980387</v>
@@ -2838,7 +2833,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C75">
         <v>630</v>
@@ -2856,10 +2851,10 @@
         <v>27.61904761904762</v>
       </c>
       <c r="H75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I75" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J75">
         <v>48.603351955307261</v>
@@ -2870,7 +2865,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C76">
         <v>1288</v>
@@ -2888,10 +2883,10 @@
         <v>2.7950310559006208</v>
       </c>
       <c r="H76" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J76">
         <v>4.6153846153846159</v>
@@ -2902,7 +2897,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C77">
         <v>2444</v>
@@ -2920,10 +2915,10 @@
         <v>4.0916530278232409E-2</v>
       </c>
       <c r="H77" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I77" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J77">
         <v>7.7942322681215898E-2</v>
@@ -2934,7 +2929,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C78">
         <v>1757</v>
@@ -2952,10 +2947,10 @@
         <v>21.684689812179851</v>
       </c>
       <c r="H78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I78" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J78">
         <v>78.234086242299796</v>
@@ -2966,7 +2961,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C79">
         <v>581</v>
@@ -2984,10 +2979,10 @@
         <v>28.05507745266781</v>
       </c>
       <c r="H79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J79">
         <v>53.267973856209153</v>
@@ -2998,7 +2993,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C80">
         <v>1247</v>
@@ -3016,10 +3011,10 @@
         <v>1.443464314354451</v>
       </c>
       <c r="H80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J80">
         <v>2.4725274725274731</v>
@@ -3030,7 +3025,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C81">
         <v>2204</v>
@@ -3048,10 +3043,10 @@
         <v>0.1361161524500907</v>
       </c>
       <c r="H81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I81" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J81">
         <v>0.2590673575129534</v>
@@ -3062,7 +3057,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C82">
         <v>970</v>
@@ -3080,10 +3075,10 @@
         <v>2.68041237113402</v>
       </c>
       <c r="H82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I82" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J82">
         <v>55.319148936170222</v>
@@ -3094,7 +3089,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C83">
         <v>184</v>
@@ -3112,10 +3107,10 @@
         <v>13.043478260869559</v>
       </c>
       <c r="H83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I83" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J83">
         <v>43.636363636363633</v>
@@ -3126,7 +3121,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C84">
         <v>347</v>
@@ -3144,10 +3139,10 @@
         <v>1.7291066282420751</v>
       </c>
       <c r="H84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I84" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J84">
         <v>3.9735099337748352</v>
@@ -3158,7 +3153,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C85">
         <v>770</v>
@@ -3176,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="H85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -3190,7 +3185,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C86">
         <v>1075</v>
@@ -3208,10 +3203,10 @@
         <v>18.697674418604649</v>
       </c>
       <c r="H86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I86" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J86">
         <v>85.897435897435898</v>
@@ -3222,7 +3217,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C87">
         <v>269</v>
@@ -3240,10 +3235,10 @@
         <v>34.572490706319712</v>
       </c>
       <c r="H87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I87" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J87">
         <v>65.957446808510639</v>
@@ -3254,7 +3249,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C88">
         <v>675</v>
@@ -3272,10 +3267,10 @@
         <v>3.8518518518518521</v>
       </c>
       <c r="H88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I88" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J88">
         <v>6.5989847715736047</v>
@@ -3286,7 +3281,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C89">
         <v>1247</v>
@@ -3304,10 +3299,10 @@
         <v>0.16038492381716121</v>
       </c>
       <c r="H89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I89" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J89">
         <v>0.30349013657056151</v>
@@ -3318,7 +3313,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C90">
         <v>1089</v>
@@ -3336,10 +3331,10 @@
         <v>28.558310376492201</v>
       </c>
       <c r="H90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J90">
         <v>91.202346041055719</v>
@@ -3350,7 +3345,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C91">
         <v>363</v>
@@ -3368,10 +3363,10 @@
         <v>40.771349862258951</v>
       </c>
       <c r="H91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J91">
         <v>72.906403940886705</v>
@@ -3382,7 +3377,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C92">
         <v>489</v>
@@ -3400,10 +3395,10 @@
         <v>3.4764826175869121</v>
       </c>
       <c r="H92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I92" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J92">
         <v>6.746031746031746</v>
@@ -3414,7 +3409,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C93">
         <v>1289</v>
@@ -3432,10 +3427,10 @@
         <v>0.23273855702094651</v>
       </c>
       <c r="H93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I93" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J93">
         <v>0.5181347150259068</v>
@@ -3446,7 +3441,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C94">
         <v>1258</v>
@@ -3464,10 +3459,10 @@
         <v>25.039745627980921</v>
       </c>
       <c r="H94" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J94">
         <v>84.677419354838719</v>
@@ -3478,7 +3473,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C95">
         <v>347</v>
@@ -3496,10 +3491,10 @@
         <v>35.73487031700288</v>
       </c>
       <c r="H95" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I95" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J95">
         <v>72.093023255813947</v>
@@ -3510,7 +3505,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C96">
         <v>532</v>
@@ -3528,10 +3523,10 @@
         <v>6.5789473684210522</v>
       </c>
       <c r="H96" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I96" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J96">
         <v>13.25757575757576</v>
@@ -3542,7 +3537,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C97">
         <v>1307</v>
@@ -3560,21 +3555,21 @@
         <v>0.22953328232593731</v>
       </c>
       <c r="H97" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J97">
         <v>0.54347826086956519</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C98">
         <v>2599</v>
@@ -3592,21 +3587,21 @@
         <v>13.158907272027699</v>
       </c>
       <c r="H98" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I98" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J98">
         <v>82.211538461538453</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C99">
         <v>1074</v>
@@ -3624,21 +3619,21 @@
         <v>20.11173184357542</v>
       </c>
       <c r="H99" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I99" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J99">
         <v>71.05263157894737</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C100">
         <v>2003</v>
@@ -3656,21 +3651,21 @@
         <v>8.1877184223664514</v>
       </c>
       <c r="H100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I100" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J100">
         <v>26.841243862520461</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C101">
         <v>3767</v>
@@ -3688,21 +3683,21 @@
         <v>0.31855588001061852</v>
       </c>
       <c r="H101" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I101" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J101">
         <v>1.191658391261172</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C102">
         <v>3093</v>
@@ -3720,21 +3715,21 @@
         <v>13.64371160685419</v>
       </c>
       <c r="H102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J102">
         <v>78.148148148148138</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C103">
         <v>1290</v>
@@ -3752,21 +3747,21 @@
         <v>21.085271317829459</v>
       </c>
       <c r="H103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J103">
         <v>75.138121546961329</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C104">
         <v>2367</v>
@@ -3784,21 +3779,21 @@
         <v>8.2805238698774826</v>
       </c>
       <c r="H104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I104" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J104">
         <v>28.44702467343977</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C105">
         <v>4074</v>
@@ -3816,21 +3811,21 @@
         <v>0.1472754050073638</v>
       </c>
       <c r="H105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I105" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J105">
         <v>0.55607043558850788</v>
       </c>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C106">
         <v>2119</v>
@@ -3848,21 +3843,21 @@
         <v>0.94384143463898063</v>
       </c>
       <c r="H106" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I106" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J106">
         <v>47.619047619047613</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C107">
         <v>693</v>
@@ -3880,21 +3875,21 @@
         <v>7.6479076479076484</v>
       </c>
       <c r="H107" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I107" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J107">
         <v>67.088607594936718</v>
       </c>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C108">
         <v>1103</v>
@@ -3912,21 +3907,21 @@
         <v>3.082502266545784</v>
       </c>
       <c r="H108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I108" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J108">
         <v>22.516556291390732</v>
       </c>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C109">
         <v>2252</v>
@@ -3944,21 +3939,21 @@
         <v>0</v>
       </c>
       <c r="H109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I109" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C110">
         <v>2767</v>
@@ -3976,21 +3971,21 @@
         <v>10.29996385977593</v>
       </c>
       <c r="H110" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I110" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J110">
         <v>77.656675749318808</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C111">
         <v>993</v>
@@ -4008,21 +4003,21 @@
         <v>17.925478348439071</v>
       </c>
       <c r="H111" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I111" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J111">
         <v>74.789915966386559</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C112">
         <v>2089</v>
@@ -4040,21 +4035,21 @@
         <v>7.7070368597415033</v>
       </c>
       <c r="H112" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I112" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J112">
         <v>24.961240310077521</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C113">
         <v>4198</v>
@@ -4072,21 +4067,21 @@
         <v>0.21438780371605529</v>
       </c>
       <c r="H113" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I113" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J113">
         <v>0.74503311258278149</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C114">
         <v>3028</v>
@@ -4104,21 +4099,21 @@
         <v>13.67239101717305</v>
       </c>
       <c r="H114" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I114" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J114">
         <v>84.146341463414629</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C115">
         <v>1320</v>
@@ -4136,21 +4131,21 @@
         <v>21.439393939393941</v>
       </c>
       <c r="H115" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I115" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J115">
         <v>76.902173913043484</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C116">
         <v>2202</v>
@@ -4168,21 +4163,21 @@
         <v>5.7220708446866482</v>
       </c>
       <c r="H116" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I116" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J116">
         <v>24.418604651162791</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C117">
         <v>4605</v>
@@ -4200,21 +4195,21 @@
         <v>0.1085776330076004</v>
       </c>
       <c r="H117" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I117" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J117">
         <v>0.43215211754537602</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118">
         <v>3079</v>
@@ -4232,21 +4227,21 @@
         <v>11.85449821370575</v>
       </c>
       <c r="H118" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I118" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J118">
         <v>82.207207207207205</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C119">
         <v>1077</v>
@@ -4264,21 +4259,21 @@
         <v>19.127205199628602</v>
       </c>
       <c r="H119" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I119" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J119">
         <v>76.865671641791039</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C120">
         <v>1943</v>
@@ -4296,21 +4291,21 @@
         <v>6.8450849202264532</v>
       </c>
       <c r="H120" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I120" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J120">
         <v>26.336633663366339</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C121">
         <v>4061</v>
@@ -4328,21 +4323,21 @@
         <v>0.17237133710908639</v>
       </c>
       <c r="H121" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I121" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J121">
         <v>0.64635272391505072</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C122">
         <v>1370</v>
@@ -4360,21 +4355,21 @@
         <v>29.34306569343066</v>
       </c>
       <c r="H122" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I122" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J122">
         <v>80.561122244488985</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C123">
         <v>522</v>
@@ -4392,21 +4387,21 @@
         <v>37.164750957854409</v>
       </c>
       <c r="H123" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I123" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J123">
         <v>72.659176029962552</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C124">
         <v>980</v>
@@ -4424,21 +4419,21 @@
         <v>17.551020408163261</v>
       </c>
       <c r="H124" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I124" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J124">
         <v>36.595744680851062</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C125">
         <v>1704</v>
@@ -4456,21 +4451,21 @@
         <v>0.41079812206572769</v>
       </c>
       <c r="H125" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J125">
         <v>1.014492753623188</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C126">
         <v>1428</v>
@@ -4488,21 +4483,21 @@
         <v>33.053221288515402</v>
       </c>
       <c r="H126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I126" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J126">
         <v>90.769230769230774</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C127">
         <v>508</v>
@@ -4520,21 +4515,21 @@
         <v>37.598425196850393</v>
       </c>
       <c r="H127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I127" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J127">
         <v>80.252100840336141</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C128">
         <v>957</v>
@@ -4552,21 +4547,21 @@
         <v>16.196447230929991</v>
       </c>
       <c r="H128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I128" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J128">
         <v>32.700421940928273</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C129">
         <v>1594</v>
@@ -4584,21 +4579,21 @@
         <v>0.62735257214554585</v>
       </c>
       <c r="H129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I129" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J129">
         <v>1.533742331288344</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C130">
         <v>931</v>
@@ -4616,21 +4611,21 @@
         <v>9.5596133190118149</v>
       </c>
       <c r="H130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I130" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J130">
         <v>76.724137931034491</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C131">
         <v>219</v>
@@ -4648,21 +4643,21 @@
         <v>10.95890410958904</v>
       </c>
       <c r="H131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I131" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J131">
         <v>58.536585365853647</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C132">
         <v>402</v>
@@ -4680,21 +4675,21 @@
         <v>5.9701492537313428</v>
       </c>
       <c r="H132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I132" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J132">
         <v>22.857142857142861</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C133">
         <v>797</v>
@@ -4712,21 +4707,21 @@
         <v>0.25094102885821828</v>
       </c>
       <c r="H133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I133" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J133">
         <v>0.81300813008130091</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C134">
         <v>1252</v>
@@ -4744,21 +4739,21 @@
         <v>34.105431309904162</v>
       </c>
       <c r="H134" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I134" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J134">
         <v>91.434689507494653</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C135">
         <v>414</v>
@@ -4776,21 +4771,21 @@
         <v>38.647342995169083</v>
       </c>
       <c r="H135" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I135" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J135">
         <v>73.732718894009224</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C136">
         <v>954</v>
@@ -4808,21 +4803,21 @@
         <v>14.67505241090147</v>
       </c>
       <c r="H136" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I136" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J136">
         <v>26.365348399246699</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C137">
         <v>1662</v>
@@ -4840,21 +4835,21 @@
         <v>0.72202166064981954</v>
       </c>
       <c r="H137" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I137" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J137">
         <v>1.294498381877023</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C138">
         <v>1523</v>
@@ -4872,21 +4867,21 @@
         <v>38.41103086014445</v>
       </c>
       <c r="H138" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I138" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J138">
         <v>92.271293375394322</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C139">
         <v>544</v>
@@ -4904,21 +4899,21 @@
         <v>46.691176470588239</v>
       </c>
       <c r="H139" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I139" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J139">
         <v>81.150159744408938</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C140">
         <v>1003</v>
@@ -4936,21 +4931,21 @@
         <v>17.347956131605191</v>
       </c>
       <c r="H140" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I140" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J140">
         <v>30.051813471502591</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C141">
         <v>1783</v>
@@ -4968,21 +4963,21 @@
         <v>0.44868199663488501</v>
       </c>
       <c r="H141" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I141" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J141">
         <v>0.91638029782359687</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C142">
         <v>1517</v>
@@ -5000,21 +4995,21 @@
         <v>36.123928806855638</v>
       </c>
       <c r="H142" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I142" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J142">
         <v>92.881355932203391</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C143">
         <v>484</v>
@@ -5032,21 +5027,21 @@
         <v>44.421487603305778</v>
       </c>
       <c r="H143" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I143" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J143">
         <v>76.512455516014228</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C144">
         <v>922</v>
@@ -5064,21 +5059,21 @@
         <v>16.485900216919742</v>
       </c>
       <c r="H144" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I144" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J144">
         <v>29.74559686888454</v>
       </c>
     </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C145">
         <v>1528</v>
@@ -5096,23 +5091,17 @@
         <v>0.52356020942408377</v>
       </c>
       <c r="H145" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I145" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J145">
         <v>1.085481682496608</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="I1:I145" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Leicester Royal"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="I1:I145" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>